--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ2.2_2.3_PH2_eval15.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ2.2_2.3_PH2_eval15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D1B42A-453E-4843-BBD8-4AC8B621F136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7FED9C-DC4A-4177-98D7-256DE60EA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32640" yWindow="4080" windowWidth="19260" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32415" yWindow="2235" windowWidth="25185" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>Variables</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>SS Target Value</t>
+  </si>
+  <si>
+    <t>Oracle Alignment</t>
+  </si>
+  <si>
+    <t>Represents the theoritical maximum achievable alignment for a probe set at a given alignment target</t>
   </si>
 </sst>
 </file>
@@ -538,21 +544,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="42.7265625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="66.26953125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="42.7265625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="66.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,28 +587,31 @@
         <v>37</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -629,28 +638,31 @@
         <v>13</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -674,27 +686,30 @@
       <c r="I3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -718,25 +733,28 @@
       <c r="I4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>23</v>
       </c>
     </row>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ2.2_2.3_PH2_eval15.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ2.2_2.3_PH2_eval15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7FED9C-DC4A-4177-98D7-256DE60EA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D903AD-DFFE-4E8A-9EFB-38A571ADE7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32415" yWindow="2235" windowWidth="25185" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,7 +170,7 @@
     <t>Oracle Alignment</t>
   </si>
   <si>
-    <t>Represents the theoritical maximum achievable alignment for a probe set at a given alignment target</t>
+    <t>Represents the theoretical maximum achievable alignment for a probe set at a given alignment target</t>
   </si>
 </sst>
 </file>
